--- a/MECSR_2027_Directory_Content_Tracker.xlsx
+++ b/MECSR_2027_Directory_Content_Tracker.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>12 Oct 2026 — sample book v13: every QR code taken out of print (listing addresses change when a listing is renamed); pages 5, 78 and 381 rewritten to match. Earlier — 10 Oct 2026 — RCM matrix of 8 Oct applied (Champion Group provisional, Ground Control, Kingdom Centre, Dhamani, Eleva AI); 04 Flat Plan moved to the v12 pagination (every spread starts on a left-hand page); intel sheets 10–12 and a book QA sheet (13) added.</t>
+          <t>13 Oct 2026 — sample book v14: Retail Congress MENA 2026 photographs on the MENA Awards page (66) and the other house ads (67–69), each showcase sponsor's own congress stand on its imagery page (21–31), and stand-ins on the Expert Views (38–54), the leadership messages (6–8) and the Title Partner page (2); the MECSR Verified seal on the 341 listings that carry a photograph and on the 7 Must-Visit pages, explained on p78. Earlier — 12 Oct 2026 — sample book v13: every QR code taken out of print (listing addresses change when a listing is renamed); pages 5, 78 and 381 rewritten to match. Earlier — 10 Oct 2026 — RCM matrix of 8 Oct applied (Champion Group provisional, Ground Control, Kingdom Centre, Dhamani, Eleva AI); 04 Flat Plan moved to the v12 pagination (every spread starts on a left-hand page); intel sheets 10–12 and a book QA sheet (13) added.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2221,7 +2220,6 @@
       <c r="M18" s="80" t="inlineStr"/>
       <c r="N18" s="80" t="inlineStr"/>
     </row>
-    <row r="19"/>
     <row r="20" ht="40" customHeight="1" s="72">
       <c r="B20" s="84" t="inlineStr">
         <is>
@@ -2296,7 +2294,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4377,7 +4374,6 @@
       <c r="I54" s="80" t="inlineStr"/>
       <c r="J54" s="80" t="inlineStr"/>
     </row>
-    <row r="55"/>
     <row r="56" ht="40" customHeight="1" s="72">
       <c r="B56" s="84" t="inlineStr">
         <is>
@@ -4433,7 +4429,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5368,7 +5363,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6021,7 +6015,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="26" customHeight="1" s="72">
       <c r="B23" s="71" t="inlineStr">
         <is>
@@ -6079,7 +6072,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6459,7 +6451,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -7205,7 +7196,11 @@
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
-      <c r="P6" s="11" t="n"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: stand-in photo (main hall, Retail Congress MENA 2026) until the title partner supplies artwork.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1" s="72">
       <c r="A7" s="8" t="n">
@@ -7421,7 +7416,11 @@
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="n"/>
       <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="n"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: congress photo below the message; the portrait is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1" s="72">
       <c r="A11" s="8" t="n">
@@ -7475,7 +7474,11 @@
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: congress photo below the message; the portrait is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1" s="72">
       <c r="A12" s="8" t="n">
@@ -7529,7 +7532,11 @@
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: congress photo below the message; the portrait is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1" s="72">
       <c r="A13" s="8" t="n">
@@ -7907,7 +7914,11 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1" s="72">
       <c r="A20" s="8" t="n">
@@ -7961,7 +7972,11 @@
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="11" t="n"/>
       <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="n"/>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="26" customHeight="1" s="72">
       <c r="A21" s="8" t="n">
@@ -8015,7 +8030,11 @@
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
-      <c r="P21" s="11" t="n"/>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1" s="72">
       <c r="A22" s="8" t="n">
@@ -8069,7 +8088,11 @@
       <c r="M22" s="11" t="n"/>
       <c r="N22" s="11" t="n"/>
       <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="n"/>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1" s="72">
       <c r="A23" s="8" t="n">
@@ -8123,7 +8146,11 @@
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="n"/>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="26" customHeight="1" s="72">
       <c r="A24" s="8" t="n">
@@ -8177,7 +8204,11 @@
       <c r="M24" s="11" t="n"/>
       <c r="N24" s="11" t="n"/>
       <c r="O24" s="11" t="n"/>
-      <c r="P24" s="11" t="n"/>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: the sponsor's own stand at Retail Congress MENA 2026 stands in for the imagery brief (right-hand page).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1" s="72">
       <c r="A25" s="8" t="n">
@@ -8393,7 +8424,11 @@
       <c r="M28" s="11" t="n"/>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="n"/>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="26" customHeight="1" s="72">
       <c r="A29" s="8" t="n">
@@ -8447,7 +8482,11 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="n"/>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="26" customHeight="1" s="72">
       <c r="A30" s="8" t="n">
@@ -8501,7 +8540,11 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
       <c r="O30" s="11" t="n"/>
-      <c r="P30" s="11" t="n"/>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="26" customHeight="1" s="72">
       <c r="A31" s="8" t="n">
@@ -8555,7 +8598,11 @@
       <c r="M31" s="11" t="n"/>
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="n"/>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1" s="72">
       <c r="A32" s="8" t="n">
@@ -8609,7 +8656,11 @@
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
       <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="n"/>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="26" customHeight="1" s="72">
       <c r="A33" s="8" t="n">
@@ -8663,7 +8714,11 @@
       <c r="M33" s="11" t="n"/>
       <c r="N33" s="11" t="n"/>
       <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="n"/>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="26" customHeight="1" s="72">
       <c r="A34" s="8" t="n">
@@ -8717,7 +8772,11 @@
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
       <c r="O34" s="11" t="n"/>
-      <c r="P34" s="11" t="n"/>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="26" customHeight="1" s="72">
       <c r="A35" s="8" t="n">
@@ -8771,7 +8830,11 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
       <c r="O35" s="11" t="n"/>
-      <c r="P35" s="11" t="n"/>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26" customHeight="1" s="72">
       <c r="A36" s="8" t="n">
@@ -8825,7 +8888,11 @@
       <c r="M36" s="11" t="n"/>
       <c r="N36" s="11" t="n"/>
       <c r="O36" s="11" t="n"/>
-      <c r="P36" s="11" t="n"/>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: a congress photo stands in for the author's supporting images; the headshot is still to be supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="26" customHeight="1" s="72">
       <c r="A37" s="8" t="n">
@@ -9149,7 +9216,11 @@
       <c r="M42" s="11" t="n"/>
       <c r="N42" s="11" t="n"/>
       <c r="O42" s="11" t="n"/>
-      <c r="P42" s="11" t="n"/>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: designed with MENA Awards 2026 photography (winners on stage).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="26" customHeight="1" s="72">
       <c r="A43" s="8" t="n">
@@ -9203,7 +9274,11 @@
       <c r="M43" s="11" t="n"/>
       <c r="N43" s="11" t="n"/>
       <c r="O43" s="11" t="n"/>
-      <c r="P43" s="11" t="n"/>
+      <c r="P43" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: designed with Retail Congress MENA 2026 photography.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="26" customHeight="1" s="72">
       <c r="A44" s="8" t="n">
@@ -9257,7 +9332,11 @@
       <c r="M44" s="11" t="n"/>
       <c r="N44" s="11" t="n"/>
       <c r="O44" s="11" t="n"/>
-      <c r="P44" s="11" t="n"/>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: designed with Retail Congress MENA 2026 photography.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="26" customHeight="1" s="72">
       <c r="A45" s="8" t="n">
@@ -9311,7 +9390,11 @@
       <c r="M45" s="11" t="n"/>
       <c r="N45" s="11" t="n"/>
       <c r="O45" s="11" t="n"/>
-      <c r="P45" s="11" t="n"/>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: designed with Retail Congress MENA 2026 photography.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="26" customHeight="1" s="72">
       <c r="A46" s="8" t="n">
@@ -9419,7 +9502,11 @@
       <c r="M47" s="11" t="n"/>
       <c r="N47" s="11" t="n"/>
       <c r="O47" s="11" t="n"/>
-      <c r="P47" s="11" t="n"/>
+      <c r="P47" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="26" customHeight="1" s="72">
       <c r="A48" s="8" t="n">
@@ -9473,7 +9560,11 @@
       <c r="M48" s="11" t="n"/>
       <c r="N48" s="11" t="n"/>
       <c r="O48" s="11" t="n"/>
-      <c r="P48" s="11" t="n"/>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="26" customHeight="1" s="72">
       <c r="A49" s="8" t="n">
@@ -9527,7 +9618,11 @@
       <c r="M49" s="11" t="n"/>
       <c r="N49" s="11" t="n"/>
       <c r="O49" s="11" t="n"/>
-      <c r="P49" s="11" t="n"/>
+      <c r="P49" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="26" customHeight="1" s="72">
       <c r="A50" s="8" t="n">
@@ -9581,7 +9676,11 @@
       <c r="M50" s="11" t="n"/>
       <c r="N50" s="11" t="n"/>
       <c r="O50" s="11" t="n"/>
-      <c r="P50" s="11" t="n"/>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="26" customHeight="1" s="72">
       <c r="A51" s="8" t="n">
@@ -9635,7 +9734,11 @@
       <c r="M51" s="11" t="n"/>
       <c r="N51" s="11" t="n"/>
       <c r="O51" s="11" t="n"/>
-      <c r="P51" s="11" t="n"/>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="26" customHeight="1" s="72">
       <c r="A52" s="8" t="n">
@@ -9689,7 +9792,11 @@
       <c r="M52" s="11" t="n"/>
       <c r="N52" s="11" t="n"/>
       <c r="O52" s="11" t="n"/>
-      <c r="P52" s="11" t="n"/>
+      <c r="P52" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="26" customHeight="1" s="72">
       <c r="A53" s="8" t="n">
@@ -9743,7 +9850,11 @@
       <c r="M53" s="11" t="n"/>
       <c r="N53" s="11" t="n"/>
       <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="n"/>
+      <c r="P53" s="11" t="inlineStr">
+        <is>
+          <t>v14 sample: MECSR Verified seal beside the centre name.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="26" customHeight="1" s="72">
       <c r="A54" s="8" t="n">
@@ -9797,7 +9908,11 @@
       <c r="M54" s="11" t="n"/>
       <c r="N54" s="11" t="n"/>
       <c r="O54" s="11" t="n"/>
-      <c r="P54" s="11" t="n"/>
+      <c r="P54" s="11" t="inlineStr">
+        <is>
+          <t>v14: legend for the MECSR Verified seal added on p78.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="26" customHeight="1" s="72">
       <c r="A55" s="8" t="n">
@@ -11903,7 +12018,11 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
       <c r="O93" s="11" t="n"/>
-      <c r="P93" s="11" t="n"/>
+      <c r="P93" s="11" t="inlineStr">
+        <is>
+          <t>v14: photography note added (RCM 2026 stand-in photos; the seal on sample listings).</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="26" customHeight="1" s="72">
       <c r="A94" s="8" t="n">
@@ -12683,7 +12802,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -13333,7 +13451,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="32" customHeight="1" s="72">
       <c r="B27" s="71" t="inlineStr">
         <is>
@@ -13398,7 +13515,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -13913,7 +14029,6 @@
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="11" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="34.05" customHeight="1" s="72">
       <c r="B15" s="71" t="inlineStr">
         <is>
@@ -13987,7 +14102,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -20064,7 +20178,6 @@
       <c r="T67" s="80" t="inlineStr"/>
       <c r="U67" s="80" t="inlineStr"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="40" customHeight="1" s="72">
       <c r="B69" s="84" t="inlineStr">
         <is>
@@ -20193,7 +20306,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="72">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -23418,7 +23530,6 @@
       <c r="O49" s="80" t="inlineStr"/>
       <c r="P49" s="80" t="inlineStr"/>
     </row>
-    <row r="50"/>
     <row r="51" ht="40" customHeight="1" s="72">
       <c r="B51" s="84" t="inlineStr">
         <is>
